--- a/DesignData/Excel_Masters/FamiliarBasicAttackStats_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarBasicAttackStats_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3f9ce60c28ea5d23/문서/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{7E267E04-52CE-4DDD-A458-4B7E6337F7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54CF4A20-B329-4C24-ABD6-7220CBCFA4E6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
+    <workbookView xWindow="900" yWindow="4185" windowWidth="28245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FamiliarBasicAttackStats" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>---</t>
   </si>
@@ -178,12 +179,15 @@
   </si>
   <si>
     <t>Usami</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/DT_ProjectileStats.DT_ProjectileStats'",RowName="Default_1Way"))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -830,6 +834,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1094,11 +1102,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1139,7 +1147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1147,13 +1155,13 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1174,7 +1182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1182,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -1209,7 +1217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1217,13 +1225,13 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>-10</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1244,7 +1252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1252,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G5">
         <v>50</v>
@@ -1276,10 +1284,10 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1287,10 +1295,10 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>50</v>
@@ -1314,7 +1322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1322,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1349,7 +1357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1357,13 +1365,13 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1384,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1392,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>50</v>
@@ -1419,7 +1427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1427,13 +1435,13 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1454,7 +1462,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1462,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>50</v>
       </c>
       <c r="G11">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1489,7 +1497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1497,13 +1505,13 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1524,7 +1532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1532,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1559,7 +1567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1567,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G14">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1594,7 +1602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1602,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1629,7 +1637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1637,10 +1645,10 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>50</v>
@@ -1661,10 +1669,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1672,13 +1680,13 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1696,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1707,10 +1715,10 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>50</v>
@@ -1734,7 +1742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -1742,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
         <v>200</v>
-      </c>
-      <c r="F19">
-        <v>50</v>
       </c>
       <c r="G19">
         <v>50</v>
@@ -1769,7 +1777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1777,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1804,7 +1812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1812,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1839,7 +1847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1847,10 +1855,10 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G22">
         <v>50</v>
@@ -1874,7 +1882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1882,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F23">
         <v>50</v>
@@ -1906,10 +1914,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1917,10 +1925,10 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G24">
         <v>50</v>
@@ -1941,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1952,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1979,7 +1987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1987,13 +1995,13 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G26">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2014,7 +2022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -2022,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2049,7 +2057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -2057,13 +2065,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G28">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2084,7 +2092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -2092,13 +2100,13 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G29">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2119,7 +2127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2127,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G30">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2154,7 +2162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -2162,13 +2170,13 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F31">
         <v>50</v>
       </c>
       <c r="G31">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2189,7 +2197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -2197,10 +2205,10 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>50</v>
@@ -2221,10 +2229,10 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2232,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G33">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2259,7 +2267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2267,13 +2275,13 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G34">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2294,7 +2302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2302,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F35">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G35">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2329,7 +2337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2337,10 +2345,10 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F36">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G36">
         <v>50</v>
@@ -2361,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2372,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F37">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G37">
         <v>50</v>
@@ -2399,7 +2407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2407,13 +2415,13 @@
         <v>1</v>
       </c>
       <c r="E38">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F38">
         <v>50</v>
       </c>
       <c r="G38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2431,10 +2439,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.6">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -2442,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F39">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
